--- a/docs/payment-schedule-templates/Payment Schedules - Customer Portal/Collection_Schedule_Template_60mo.xlsx
+++ b/docs/payment-schedule-templates/Payment Schedules - Customer Portal/Collection_Schedule_Template_60mo.xlsx
@@ -1187,20 +1187,55 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="14">
-      <c r="A2" s="20" t="n"/>
-      <c r="B2" s="20" t="n"/>
-      <c r="C2" s="20" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="21" t="n"/>
-      <c r="H2" s="21" t="n"/>
-      <c r="I2" s="21" t="n"/>
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>{{########}}</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Nyandoro</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>+17785808657</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>alex@michaeltenable.com</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>Internal Tester</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I2" s="21" t="n">
+        <v>120000</v>
+      </c>
       <c r="J2" s="22" t="n">
         <v>60</v>
       </c>
-      <c r="K2" s="21" t="n"/>
-      <c r="L2" s="23" t="n"/>
+      <c r="K2" s="21">
+        <f>IF(J2=0,"",ROUND((I2-H2)/J2,2))</f>
+        <v/>
+      </c>
+      <c r="L2" s="23" t="n">
+        <v>46147</v>
+      </c>
       <c r="M2" s="21" t="n"/>
       <c r="N2" s="21" t="n"/>
       <c r="O2" s="21" t="n"/>
@@ -1263,15 +1298,15 @@
       <c r="BT2" s="21" t="n"/>
       <c r="BU2" s="21" t="n"/>
       <c r="BV2" s="24">
-        <f>SUM(M2:BT2)</f>
+        <f>H2+SUM(M2:BT2)</f>
         <v/>
       </c>
       <c r="BW2" s="24">
-        <f>I2-BV2</f>
+        <f>I2-H2-SUM(M2:BT2)</f>
         <v/>
       </c>
       <c r="BX2" s="25">
-        <f>IF(I2=0,"",BV2/I2)</f>
+        <f>IF(I2=0,"",(H2+SUM(M2:BT2))/I2)</f>
         <v/>
       </c>
       <c r="BY2" s="26" t="n"/>
@@ -1360,15 +1395,15 @@
       <c r="BT3" s="21" t="n"/>
       <c r="BU3" s="21" t="n"/>
       <c r="BV3" s="24">
-        <f>SUM(M3:BT3)</f>
+        <f>H3+SUM(M3:BT3)</f>
         <v/>
       </c>
       <c r="BW3" s="24">
-        <f>I3-BV3</f>
+        <f>I3-H3-SUM(M3:BT3)</f>
         <v/>
       </c>
       <c r="BX3" s="25">
-        <f>IF(I3=0,"",BV3/I3)</f>
+        <f>IF(I3=0,"",(H3+SUM(M3:BT3))/I3)</f>
         <v/>
       </c>
       <c r="BY3" s="26" t="n"/>
@@ -1457,15 +1492,15 @@
       <c r="BT4" s="21" t="n"/>
       <c r="BU4" s="21" t="n"/>
       <c r="BV4" s="24">
-        <f>SUM(M4:BT4)</f>
+        <f>H4+SUM(M4:BT4)</f>
         <v/>
       </c>
       <c r="BW4" s="24">
-        <f>I4-BV4</f>
+        <f>I4-H4-SUM(M4:BT4)</f>
         <v/>
       </c>
       <c r="BX4" s="25">
-        <f>IF(I4=0,"",BV4/I4)</f>
+        <f>IF(I4=0,"",(H4+SUM(M4:BT4))/I4)</f>
         <v/>
       </c>
       <c r="BY4" s="26" t="n"/>
@@ -1554,15 +1589,15 @@
       <c r="BT5" s="21" t="n"/>
       <c r="BU5" s="21" t="n"/>
       <c r="BV5" s="24">
-        <f>SUM(M5:BT5)</f>
+        <f>H5+SUM(M5:BT5)</f>
         <v/>
       </c>
       <c r="BW5" s="24">
-        <f>I5-BV5</f>
+        <f>I5-H5-SUM(M5:BT5)</f>
         <v/>
       </c>
       <c r="BX5" s="25">
-        <f>IF(I5=0,"",BV5/I5)</f>
+        <f>IF(I5=0,"",(H5+SUM(M5:BT5))/I5)</f>
         <v/>
       </c>
       <c r="BY5" s="26" t="n"/>
@@ -1651,15 +1686,15 @@
       <c r="BT6" s="21" t="n"/>
       <c r="BU6" s="21" t="n"/>
       <c r="BV6" s="24">
-        <f>SUM(M6:BT6)</f>
+        <f>H6+SUM(M6:BT6)</f>
         <v/>
       </c>
       <c r="BW6" s="24">
-        <f>I6-BV6</f>
+        <f>I6-H6-SUM(M6:BT6)</f>
         <v/>
       </c>
       <c r="BX6" s="25">
-        <f>IF(I6=0,"",BV6/I6)</f>
+        <f>IF(I6=0,"",(H6+SUM(M6:BT6))/I6)</f>
         <v/>
       </c>
       <c r="BY6" s="26" t="n"/>
@@ -1748,15 +1783,15 @@
       <c r="BT7" s="21" t="n"/>
       <c r="BU7" s="21" t="n"/>
       <c r="BV7" s="24">
-        <f>SUM(M7:BT7)</f>
+        <f>H7+SUM(M7:BT7)</f>
         <v/>
       </c>
       <c r="BW7" s="24">
-        <f>I7-BV7</f>
+        <f>I7-H7-SUM(M7:BT7)</f>
         <v/>
       </c>
       <c r="BX7" s="25">
-        <f>IF(I7=0,"",BV7/I7)</f>
+        <f>IF(I7=0,"",(H7+SUM(M7:BT7))/I7)</f>
         <v/>
       </c>
       <c r="BY7" s="26" t="n"/>
@@ -1845,15 +1880,15 @@
       <c r="BT8" s="21" t="n"/>
       <c r="BU8" s="21" t="n"/>
       <c r="BV8" s="24">
-        <f>SUM(M8:BT8)</f>
+        <f>H8+SUM(M8:BT8)</f>
         <v/>
       </c>
       <c r="BW8" s="24">
-        <f>I8-BV8</f>
+        <f>I8-H8-SUM(M8:BT8)</f>
         <v/>
       </c>
       <c r="BX8" s="25">
-        <f>IF(I8=0,"",BV8/I8)</f>
+        <f>IF(I8=0,"",(H8+SUM(M8:BT8))/I8)</f>
         <v/>
       </c>
       <c r="BY8" s="26" t="n"/>
@@ -1942,15 +1977,15 @@
       <c r="BT9" s="21" t="n"/>
       <c r="BU9" s="21" t="n"/>
       <c r="BV9" s="24">
-        <f>SUM(M9:BT9)</f>
+        <f>H9+SUM(M9:BT9)</f>
         <v/>
       </c>
       <c r="BW9" s="24">
-        <f>I9-BV9</f>
+        <f>I9-H9-SUM(M9:BT9)</f>
         <v/>
       </c>
       <c r="BX9" s="25">
-        <f>IF(I9=0,"",BV9/I9)</f>
+        <f>IF(I9=0,"",(H9+SUM(M9:BT9))/I9)</f>
         <v/>
       </c>
       <c r="BY9" s="26" t="n"/>
@@ -2039,15 +2074,15 @@
       <c r="BT10" s="21" t="n"/>
       <c r="BU10" s="21" t="n"/>
       <c r="BV10" s="24">
-        <f>SUM(M10:BT10)</f>
+        <f>H10+SUM(M10:BT10)</f>
         <v/>
       </c>
       <c r="BW10" s="24">
-        <f>I10-BV10</f>
+        <f>I10-H10-SUM(M10:BT10)</f>
         <v/>
       </c>
       <c r="BX10" s="25">
-        <f>IF(I10=0,"",BV10/I10)</f>
+        <f>IF(I10=0,"",(H10+SUM(M10:BT10))/I10)</f>
         <v/>
       </c>
       <c r="BY10" s="26" t="n"/>
@@ -2136,15 +2171,15 @@
       <c r="BT11" s="21" t="n"/>
       <c r="BU11" s="21" t="n"/>
       <c r="BV11" s="24">
-        <f>SUM(M11:BT11)</f>
+        <f>H11+SUM(M11:BT11)</f>
         <v/>
       </c>
       <c r="BW11" s="24">
-        <f>I11-BV11</f>
+        <f>I11-H11-SUM(M11:BT11)</f>
         <v/>
       </c>
       <c r="BX11" s="25">
-        <f>IF(I11=0,"",BV11/I11)</f>
+        <f>IF(I11=0,"",(H11+SUM(M11:BT11))/I11)</f>
         <v/>
       </c>
       <c r="BY11" s="26" t="n"/>
@@ -2233,15 +2268,15 @@
       <c r="BT12" s="21" t="n"/>
       <c r="BU12" s="21" t="n"/>
       <c r="BV12" s="24">
-        <f>SUM(M12:BT12)</f>
+        <f>H12+SUM(M12:BT12)</f>
         <v/>
       </c>
       <c r="BW12" s="24">
-        <f>I12-BV12</f>
+        <f>I12-H12-SUM(M12:BT12)</f>
         <v/>
       </c>
       <c r="BX12" s="25">
-        <f>IF(I12=0,"",BV12/I12)</f>
+        <f>IF(I12=0,"",(H12+SUM(M12:BT12))/I12)</f>
         <v/>
       </c>
       <c r="BY12" s="26" t="n"/>
@@ -2330,15 +2365,15 @@
       <c r="BT13" s="21" t="n"/>
       <c r="BU13" s="21" t="n"/>
       <c r="BV13" s="24">
-        <f>SUM(M13:BT13)</f>
+        <f>H13+SUM(M13:BT13)</f>
         <v/>
       </c>
       <c r="BW13" s="24">
-        <f>I13-BV13</f>
+        <f>I13-H13-SUM(M13:BT13)</f>
         <v/>
       </c>
       <c r="BX13" s="25">
-        <f>IF(I13=0,"",BV13/I13)</f>
+        <f>IF(I13=0,"",(H13+SUM(M13:BT13))/I13)</f>
         <v/>
       </c>
       <c r="BY13" s="26" t="n"/>
@@ -2427,15 +2462,15 @@
       <c r="BT14" s="21" t="n"/>
       <c r="BU14" s="21" t="n"/>
       <c r="BV14" s="24">
-        <f>SUM(M14:BT14)</f>
+        <f>H14+SUM(M14:BT14)</f>
         <v/>
       </c>
       <c r="BW14" s="24">
-        <f>I14-BV14</f>
+        <f>I14-H14-SUM(M14:BT14)</f>
         <v/>
       </c>
       <c r="BX14" s="25">
-        <f>IF(I14=0,"",BV14/I14)</f>
+        <f>IF(I14=0,"",(H14+SUM(M14:BT14))/I14)</f>
         <v/>
       </c>
       <c r="BY14" s="26" t="n"/>
@@ -2524,15 +2559,15 @@
       <c r="BT15" s="21" t="n"/>
       <c r="BU15" s="21" t="n"/>
       <c r="BV15" s="24">
-        <f>SUM(M15:BT15)</f>
+        <f>H15+SUM(M15:BT15)</f>
         <v/>
       </c>
       <c r="BW15" s="24">
-        <f>I15-BV15</f>
+        <f>I15-H15-SUM(M15:BT15)</f>
         <v/>
       </c>
       <c r="BX15" s="25">
-        <f>IF(I15=0,"",BV15/I15)</f>
+        <f>IF(I15=0,"",(H15+SUM(M15:BT15))/I15)</f>
         <v/>
       </c>
       <c r="BY15" s="26" t="n"/>
@@ -2621,15 +2656,15 @@
       <c r="BT16" s="21" t="n"/>
       <c r="BU16" s="21" t="n"/>
       <c r="BV16" s="24">
-        <f>SUM(M16:BT16)</f>
+        <f>H16+SUM(M16:BT16)</f>
         <v/>
       </c>
       <c r="BW16" s="24">
-        <f>I16-BV16</f>
+        <f>I16-H16-SUM(M16:BT16)</f>
         <v/>
       </c>
       <c r="BX16" s="25">
-        <f>IF(I16=0,"",BV16/I16)</f>
+        <f>IF(I16=0,"",(H16+SUM(M16:BT16))/I16)</f>
         <v/>
       </c>
       <c r="BY16" s="26" t="n"/>
@@ -2718,15 +2753,15 @@
       <c r="BT17" s="21" t="n"/>
       <c r="BU17" s="21" t="n"/>
       <c r="BV17" s="24">
-        <f>SUM(M17:BT17)</f>
+        <f>H17+SUM(M17:BT17)</f>
         <v/>
       </c>
       <c r="BW17" s="24">
-        <f>I17-BV17</f>
+        <f>I17-H17-SUM(M17:BT17)</f>
         <v/>
       </c>
       <c r="BX17" s="25">
-        <f>IF(I17=0,"",BV17/I17)</f>
+        <f>IF(I17=0,"",(H17+SUM(M17:BT17))/I17)</f>
         <v/>
       </c>
       <c r="BY17" s="26" t="n"/>
@@ -2815,15 +2850,15 @@
       <c r="BT18" s="21" t="n"/>
       <c r="BU18" s="21" t="n"/>
       <c r="BV18" s="24">
-        <f>SUM(M18:BT18)</f>
+        <f>H18+SUM(M18:BT18)</f>
         <v/>
       </c>
       <c r="BW18" s="24">
-        <f>I18-BV18</f>
+        <f>I18-H18-SUM(M18:BT18)</f>
         <v/>
       </c>
       <c r="BX18" s="25">
-        <f>IF(I18=0,"",BV18/I18)</f>
+        <f>IF(I18=0,"",(H18+SUM(M18:BT18))/I18)</f>
         <v/>
       </c>
       <c r="BY18" s="26" t="n"/>
@@ -2912,15 +2947,15 @@
       <c r="BT19" s="21" t="n"/>
       <c r="BU19" s="21" t="n"/>
       <c r="BV19" s="24">
-        <f>SUM(M19:BT19)</f>
+        <f>H19+SUM(M19:BT19)</f>
         <v/>
       </c>
       <c r="BW19" s="24">
-        <f>I19-BV19</f>
+        <f>I19-H19-SUM(M19:BT19)</f>
         <v/>
       </c>
       <c r="BX19" s="25">
-        <f>IF(I19=0,"",BV19/I19)</f>
+        <f>IF(I19=0,"",(H19+SUM(M19:BT19))/I19)</f>
         <v/>
       </c>
       <c r="BY19" s="26" t="n"/>
@@ -3009,15 +3044,15 @@
       <c r="BT20" s="21" t="n"/>
       <c r="BU20" s="21" t="n"/>
       <c r="BV20" s="24">
-        <f>SUM(M20:BT20)</f>
+        <f>H20+SUM(M20:BT20)</f>
         <v/>
       </c>
       <c r="BW20" s="24">
-        <f>I20-BV20</f>
+        <f>I20-H20-SUM(M20:BT20)</f>
         <v/>
       </c>
       <c r="BX20" s="25">
-        <f>IF(I20=0,"",BV20/I20)</f>
+        <f>IF(I20=0,"",(H20+SUM(M20:BT20))/I20)</f>
         <v/>
       </c>
       <c r="BY20" s="26" t="n"/>
@@ -3106,15 +3141,15 @@
       <c r="BT21" s="21" t="n"/>
       <c r="BU21" s="21" t="n"/>
       <c r="BV21" s="24">
-        <f>SUM(M21:BT21)</f>
+        <f>H21+SUM(M21:BT21)</f>
         <v/>
       </c>
       <c r="BW21" s="24">
-        <f>I21-BV21</f>
+        <f>I21-H21-SUM(M21:BT21)</f>
         <v/>
       </c>
       <c r="BX21" s="25">
-        <f>IF(I21=0,"",BV21/I21)</f>
+        <f>IF(I21=0,"",(H21+SUM(M21:BT21))/I21)</f>
         <v/>
       </c>
       <c r="BY21" s="26" t="n"/>
@@ -3203,15 +3238,15 @@
       <c r="BT22" s="21" t="n"/>
       <c r="BU22" s="21" t="n"/>
       <c r="BV22" s="24">
-        <f>SUM(M22:BT22)</f>
+        <f>H22+SUM(M22:BT22)</f>
         <v/>
       </c>
       <c r="BW22" s="24">
-        <f>I22-BV22</f>
+        <f>I22-H22-SUM(M22:BT22)</f>
         <v/>
       </c>
       <c r="BX22" s="25">
-        <f>IF(I22=0,"",BV22/I22)</f>
+        <f>IF(I22=0,"",(H22+SUM(M22:BT22))/I22)</f>
         <v/>
       </c>
       <c r="BY22" s="26" t="n"/>
@@ -3300,15 +3335,15 @@
       <c r="BT23" s="21" t="n"/>
       <c r="BU23" s="21" t="n"/>
       <c r="BV23" s="24">
-        <f>SUM(M23:BT23)</f>
+        <f>H23+SUM(M23:BT23)</f>
         <v/>
       </c>
       <c r="BW23" s="24">
-        <f>I23-BV23</f>
+        <f>I23-H23-SUM(M23:BT23)</f>
         <v/>
       </c>
       <c r="BX23" s="25">
-        <f>IF(I23=0,"",BV23/I23)</f>
+        <f>IF(I23=0,"",(H23+SUM(M23:BT23))/I23)</f>
         <v/>
       </c>
       <c r="BY23" s="26" t="n"/>
@@ -3397,15 +3432,15 @@
       <c r="BT24" s="21" t="n"/>
       <c r="BU24" s="21" t="n"/>
       <c r="BV24" s="24">
-        <f>SUM(M24:BT24)</f>
+        <f>H24+SUM(M24:BT24)</f>
         <v/>
       </c>
       <c r="BW24" s="24">
-        <f>I24-BV24</f>
+        <f>I24-H24-SUM(M24:BT24)</f>
         <v/>
       </c>
       <c r="BX24" s="25">
-        <f>IF(I24=0,"",BV24/I24)</f>
+        <f>IF(I24=0,"",(H24+SUM(M24:BT24))/I24)</f>
         <v/>
       </c>
       <c r="BY24" s="26" t="n"/>
@@ -3494,15 +3529,15 @@
       <c r="BT25" s="21" t="n"/>
       <c r="BU25" s="21" t="n"/>
       <c r="BV25" s="24">
-        <f>SUM(M25:BT25)</f>
+        <f>H25+SUM(M25:BT25)</f>
         <v/>
       </c>
       <c r="BW25" s="24">
-        <f>I25-BV25</f>
+        <f>I25-H25-SUM(M25:BT25)</f>
         <v/>
       </c>
       <c r="BX25" s="25">
-        <f>IF(I25=0,"",BV25/I25)</f>
+        <f>IF(I25=0,"",(H25+SUM(M25:BT25))/I25)</f>
         <v/>
       </c>
       <c r="BY25" s="26" t="n"/>
@@ -3591,15 +3626,15 @@
       <c r="BT26" s="21" t="n"/>
       <c r="BU26" s="21" t="n"/>
       <c r="BV26" s="24">
-        <f>SUM(M26:BT26)</f>
+        <f>H26+SUM(M26:BT26)</f>
         <v/>
       </c>
       <c r="BW26" s="24">
-        <f>I26-BV26</f>
+        <f>I26-H26-SUM(M26:BT26)</f>
         <v/>
       </c>
       <c r="BX26" s="25">
-        <f>IF(I26=0,"",BV26/I26)</f>
+        <f>IF(I26=0,"",(H26+SUM(M26:BT26))/I26)</f>
         <v/>
       </c>
       <c r="BY26" s="26" t="n"/>
@@ -3688,15 +3723,15 @@
       <c r="BT27" s="21" t="n"/>
       <c r="BU27" s="21" t="n"/>
       <c r="BV27" s="24">
-        <f>SUM(M27:BT27)</f>
+        <f>H27+SUM(M27:BT27)</f>
         <v/>
       </c>
       <c r="BW27" s="24">
-        <f>I27-BV27</f>
+        <f>I27-H27-SUM(M27:BT27)</f>
         <v/>
       </c>
       <c r="BX27" s="25">
-        <f>IF(I27=0,"",BV27/I27)</f>
+        <f>IF(I27=0,"",(H27+SUM(M27:BT27))/I27)</f>
         <v/>
       </c>
       <c r="BY27" s="26" t="n"/>
@@ -3785,15 +3820,15 @@
       <c r="BT28" s="21" t="n"/>
       <c r="BU28" s="21" t="n"/>
       <c r="BV28" s="24">
-        <f>SUM(M28:BT28)</f>
+        <f>H28+SUM(M28:BT28)</f>
         <v/>
       </c>
       <c r="BW28" s="24">
-        <f>I28-BV28</f>
+        <f>I28-H28-SUM(M28:BT28)</f>
         <v/>
       </c>
       <c r="BX28" s="25">
-        <f>IF(I28=0,"",BV28/I28)</f>
+        <f>IF(I28=0,"",(H28+SUM(M28:BT28))/I28)</f>
         <v/>
       </c>
       <c r="BY28" s="26" t="n"/>
@@ -3882,15 +3917,15 @@
       <c r="BT29" s="21" t="n"/>
       <c r="BU29" s="21" t="n"/>
       <c r="BV29" s="24">
-        <f>SUM(M29:BT29)</f>
+        <f>H29+SUM(M29:BT29)</f>
         <v/>
       </c>
       <c r="BW29" s="24">
-        <f>I29-BV29</f>
+        <f>I29-H29-SUM(M29:BT29)</f>
         <v/>
       </c>
       <c r="BX29" s="25">
-        <f>IF(I29=0,"",BV29/I29)</f>
+        <f>IF(I29=0,"",(H29+SUM(M29:BT29))/I29)</f>
         <v/>
       </c>
       <c r="BY29" s="26" t="n"/>
@@ -3979,15 +4014,15 @@
       <c r="BT30" s="21" t="n"/>
       <c r="BU30" s="21" t="n"/>
       <c r="BV30" s="24">
-        <f>SUM(M30:BT30)</f>
+        <f>H30+SUM(M30:BT30)</f>
         <v/>
       </c>
       <c r="BW30" s="24">
-        <f>I30-BV30</f>
+        <f>I30-H30-SUM(M30:BT30)</f>
         <v/>
       </c>
       <c r="BX30" s="25">
-        <f>IF(I30=0,"",BV30/I30)</f>
+        <f>IF(I30=0,"",(H30+SUM(M30:BT30))/I30)</f>
         <v/>
       </c>
       <c r="BY30" s="26" t="n"/>
@@ -4076,15 +4111,15 @@
       <c r="BT31" s="21" t="n"/>
       <c r="BU31" s="21" t="n"/>
       <c r="BV31" s="24">
-        <f>SUM(M31:BT31)</f>
+        <f>H31+SUM(M31:BT31)</f>
         <v/>
       </c>
       <c r="BW31" s="24">
-        <f>I31-BV31</f>
+        <f>I31-H31-SUM(M31:BT31)</f>
         <v/>
       </c>
       <c r="BX31" s="25">
-        <f>IF(I31=0,"",BV31/I31)</f>
+        <f>IF(I31=0,"",(H31+SUM(M31:BT31))/I31)</f>
         <v/>
       </c>
       <c r="BY31" s="26" t="n"/>
@@ -4173,15 +4208,15 @@
       <c r="BT32" s="21" t="n"/>
       <c r="BU32" s="21" t="n"/>
       <c r="BV32" s="24">
-        <f>SUM(M32:BT32)</f>
+        <f>H32+SUM(M32:BT32)</f>
         <v/>
       </c>
       <c r="BW32" s="24">
-        <f>I32-BV32</f>
+        <f>I32-H32-SUM(M32:BT32)</f>
         <v/>
       </c>
       <c r="BX32" s="25">
-        <f>IF(I32=0,"",BV32/I32)</f>
+        <f>IF(I32=0,"",(H32+SUM(M32:BT32))/I32)</f>
         <v/>
       </c>
       <c r="BY32" s="26" t="n"/>
@@ -4270,15 +4305,15 @@
       <c r="BT33" s="21" t="n"/>
       <c r="BU33" s="21" t="n"/>
       <c r="BV33" s="24">
-        <f>SUM(M33:BT33)</f>
+        <f>H33+SUM(M33:BT33)</f>
         <v/>
       </c>
       <c r="BW33" s="24">
-        <f>I33-BV33</f>
+        <f>I33-H33-SUM(M33:BT33)</f>
         <v/>
       </c>
       <c r="BX33" s="25">
-        <f>IF(I33=0,"",BV33/I33)</f>
+        <f>IF(I33=0,"",(H33+SUM(M33:BT33))/I33)</f>
         <v/>
       </c>
       <c r="BY33" s="26" t="n"/>
@@ -4367,15 +4402,15 @@
       <c r="BT34" s="21" t="n"/>
       <c r="BU34" s="21" t="n"/>
       <c r="BV34" s="24">
-        <f>SUM(M34:BT34)</f>
+        <f>H34+SUM(M34:BT34)</f>
         <v/>
       </c>
       <c r="BW34" s="24">
-        <f>I34-BV34</f>
+        <f>I34-H34-SUM(M34:BT34)</f>
         <v/>
       </c>
       <c r="BX34" s="25">
-        <f>IF(I34=0,"",BV34/I34)</f>
+        <f>IF(I34=0,"",(H34+SUM(M34:BT34))/I34)</f>
         <v/>
       </c>
       <c r="BY34" s="26" t="n"/>
@@ -4464,15 +4499,15 @@
       <c r="BT35" s="21" t="n"/>
       <c r="BU35" s="21" t="n"/>
       <c r="BV35" s="24">
-        <f>SUM(M35:BT35)</f>
+        <f>H35+SUM(M35:BT35)</f>
         <v/>
       </c>
       <c r="BW35" s="24">
-        <f>I35-BV35</f>
+        <f>I35-H35-SUM(M35:BT35)</f>
         <v/>
       </c>
       <c r="BX35" s="25">
-        <f>IF(I35=0,"",BV35/I35)</f>
+        <f>IF(I35=0,"",(H35+SUM(M35:BT35))/I35)</f>
         <v/>
       </c>
       <c r="BY35" s="26" t="n"/>
@@ -4561,15 +4596,15 @@
       <c r="BT36" s="21" t="n"/>
       <c r="BU36" s="21" t="n"/>
       <c r="BV36" s="24">
-        <f>SUM(M36:BT36)</f>
+        <f>H36+SUM(M36:BT36)</f>
         <v/>
       </c>
       <c r="BW36" s="24">
-        <f>I36-BV36</f>
+        <f>I36-H36-SUM(M36:BT36)</f>
         <v/>
       </c>
       <c r="BX36" s="25">
-        <f>IF(I36=0,"",BV36/I36)</f>
+        <f>IF(I36=0,"",(H36+SUM(M36:BT36))/I36)</f>
         <v/>
       </c>
       <c r="BY36" s="26" t="n"/>
@@ -4658,15 +4693,15 @@
       <c r="BT37" s="21" t="n"/>
       <c r="BU37" s="21" t="n"/>
       <c r="BV37" s="24">
-        <f>SUM(M37:BT37)</f>
+        <f>H37+SUM(M37:BT37)</f>
         <v/>
       </c>
       <c r="BW37" s="24">
-        <f>I37-BV37</f>
+        <f>I37-H37-SUM(M37:BT37)</f>
         <v/>
       </c>
       <c r="BX37" s="25">
-        <f>IF(I37=0,"",BV37/I37)</f>
+        <f>IF(I37=0,"",(H37+SUM(M37:BT37))/I37)</f>
         <v/>
       </c>
       <c r="BY37" s="26" t="n"/>
@@ -4755,15 +4790,15 @@
       <c r="BT38" s="21" t="n"/>
       <c r="BU38" s="21" t="n"/>
       <c r="BV38" s="24">
-        <f>SUM(M38:BT38)</f>
+        <f>H38+SUM(M38:BT38)</f>
         <v/>
       </c>
       <c r="BW38" s="24">
-        <f>I38-BV38</f>
+        <f>I38-H38-SUM(M38:BT38)</f>
         <v/>
       </c>
       <c r="BX38" s="25">
-        <f>IF(I38=0,"",BV38/I38)</f>
+        <f>IF(I38=0,"",(H38+SUM(M38:BT38))/I38)</f>
         <v/>
       </c>
       <c r="BY38" s="26" t="n"/>
@@ -4852,15 +4887,15 @@
       <c r="BT39" s="21" t="n"/>
       <c r="BU39" s="21" t="n"/>
       <c r="BV39" s="24">
-        <f>SUM(M39:BT39)</f>
+        <f>H39+SUM(M39:BT39)</f>
         <v/>
       </c>
       <c r="BW39" s="24">
-        <f>I39-BV39</f>
+        <f>I39-H39-SUM(M39:BT39)</f>
         <v/>
       </c>
       <c r="BX39" s="25">
-        <f>IF(I39=0,"",BV39/I39)</f>
+        <f>IF(I39=0,"",(H39+SUM(M39:BT39))/I39)</f>
         <v/>
       </c>
       <c r="BY39" s="26" t="n"/>
@@ -4949,15 +4984,15 @@
       <c r="BT40" s="21" t="n"/>
       <c r="BU40" s="21" t="n"/>
       <c r="BV40" s="24">
-        <f>SUM(M40:BT40)</f>
+        <f>H40+SUM(M40:BT40)</f>
         <v/>
       </c>
       <c r="BW40" s="24">
-        <f>I40-BV40</f>
+        <f>I40-H40-SUM(M40:BT40)</f>
         <v/>
       </c>
       <c r="BX40" s="25">
-        <f>IF(I40=0,"",BV40/I40)</f>
+        <f>IF(I40=0,"",(H40+SUM(M40:BT40))/I40)</f>
         <v/>
       </c>
       <c r="BY40" s="26" t="n"/>
@@ -5046,15 +5081,15 @@
       <c r="BT41" s="21" t="n"/>
       <c r="BU41" s="21" t="n"/>
       <c r="BV41" s="24">
-        <f>SUM(M41:BT41)</f>
+        <f>H41+SUM(M41:BT41)</f>
         <v/>
       </c>
       <c r="BW41" s="24">
-        <f>I41-BV41</f>
+        <f>I41-H41-SUM(M41:BT41)</f>
         <v/>
       </c>
       <c r="BX41" s="25">
-        <f>IF(I41=0,"",BV41/I41)</f>
+        <f>IF(I41=0,"",(H41+SUM(M41:BT41))/I41)</f>
         <v/>
       </c>
       <c r="BY41" s="26" t="n"/>
@@ -5143,15 +5178,15 @@
       <c r="BT42" s="21" t="n"/>
       <c r="BU42" s="21" t="n"/>
       <c r="BV42" s="24">
-        <f>SUM(M42:BT42)</f>
+        <f>H42+SUM(M42:BT42)</f>
         <v/>
       </c>
       <c r="BW42" s="24">
-        <f>I42-BV42</f>
+        <f>I42-H42-SUM(M42:BT42)</f>
         <v/>
       </c>
       <c r="BX42" s="25">
-        <f>IF(I42=0,"",BV42/I42)</f>
+        <f>IF(I42=0,"",(H42+SUM(M42:BT42))/I42)</f>
         <v/>
       </c>
       <c r="BY42" s="26" t="n"/>
@@ -5240,15 +5275,15 @@
       <c r="BT43" s="21" t="n"/>
       <c r="BU43" s="21" t="n"/>
       <c r="BV43" s="24">
-        <f>SUM(M43:BT43)</f>
+        <f>H43+SUM(M43:BT43)</f>
         <v/>
       </c>
       <c r="BW43" s="24">
-        <f>I43-BV43</f>
+        <f>I43-H43-SUM(M43:BT43)</f>
         <v/>
       </c>
       <c r="BX43" s="25">
-        <f>IF(I43=0,"",BV43/I43)</f>
+        <f>IF(I43=0,"",(H43+SUM(M43:BT43))/I43)</f>
         <v/>
       </c>
       <c r="BY43" s="26" t="n"/>
@@ -5337,15 +5372,15 @@
       <c r="BT44" s="21" t="n"/>
       <c r="BU44" s="21" t="n"/>
       <c r="BV44" s="24">
-        <f>SUM(M44:BT44)</f>
+        <f>H44+SUM(M44:BT44)</f>
         <v/>
       </c>
       <c r="BW44" s="24">
-        <f>I44-BV44</f>
+        <f>I44-H44-SUM(M44:BT44)</f>
         <v/>
       </c>
       <c r="BX44" s="25">
-        <f>IF(I44=0,"",BV44/I44)</f>
+        <f>IF(I44=0,"",(H44+SUM(M44:BT44))/I44)</f>
         <v/>
       </c>
       <c r="BY44" s="26" t="n"/>
@@ -5434,15 +5469,15 @@
       <c r="BT45" s="21" t="n"/>
       <c r="BU45" s="21" t="n"/>
       <c r="BV45" s="24">
-        <f>SUM(M45:BT45)</f>
+        <f>H45+SUM(M45:BT45)</f>
         <v/>
       </c>
       <c r="BW45" s="24">
-        <f>I45-BV45</f>
+        <f>I45-H45-SUM(M45:BT45)</f>
         <v/>
       </c>
       <c r="BX45" s="25">
-        <f>IF(I45=0,"",BV45/I45)</f>
+        <f>IF(I45=0,"",(H45+SUM(M45:BT45))/I45)</f>
         <v/>
       </c>
       <c r="BY45" s="26" t="n"/>
@@ -5531,15 +5566,15 @@
       <c r="BT46" s="21" t="n"/>
       <c r="BU46" s="21" t="n"/>
       <c r="BV46" s="24">
-        <f>SUM(M46:BT46)</f>
+        <f>H46+SUM(M46:BT46)</f>
         <v/>
       </c>
       <c r="BW46" s="24">
-        <f>I46-BV46</f>
+        <f>I46-H46-SUM(M46:BT46)</f>
         <v/>
       </c>
       <c r="BX46" s="25">
-        <f>IF(I46=0,"",BV46/I46)</f>
+        <f>IF(I46=0,"",(H46+SUM(M46:BT46))/I46)</f>
         <v/>
       </c>
       <c r="BY46" s="26" t="n"/>
@@ -5628,15 +5663,15 @@
       <c r="BT47" s="21" t="n"/>
       <c r="BU47" s="21" t="n"/>
       <c r="BV47" s="24">
-        <f>SUM(M47:BT47)</f>
+        <f>H47+SUM(M47:BT47)</f>
         <v/>
       </c>
       <c r="BW47" s="24">
-        <f>I47-BV47</f>
+        <f>I47-H47-SUM(M47:BT47)</f>
         <v/>
       </c>
       <c r="BX47" s="25">
-        <f>IF(I47=0,"",BV47/I47)</f>
+        <f>IF(I47=0,"",(H47+SUM(M47:BT47))/I47)</f>
         <v/>
       </c>
       <c r="BY47" s="26" t="n"/>
@@ -5725,15 +5760,15 @@
       <c r="BT48" s="21" t="n"/>
       <c r="BU48" s="21" t="n"/>
       <c r="BV48" s="24">
-        <f>SUM(M48:BT48)</f>
+        <f>H48+SUM(M48:BT48)</f>
         <v/>
       </c>
       <c r="BW48" s="24">
-        <f>I48-BV48</f>
+        <f>I48-H48-SUM(M48:BT48)</f>
         <v/>
       </c>
       <c r="BX48" s="25">
-        <f>IF(I48=0,"",BV48/I48)</f>
+        <f>IF(I48=0,"",(H48+SUM(M48:BT48))/I48)</f>
         <v/>
       </c>
       <c r="BY48" s="26" t="n"/>
@@ -5822,15 +5857,15 @@
       <c r="BT49" s="21" t="n"/>
       <c r="BU49" s="21" t="n"/>
       <c r="BV49" s="24">
-        <f>SUM(M49:BT49)</f>
+        <f>H49+SUM(M49:BT49)</f>
         <v/>
       </c>
       <c r="BW49" s="24">
-        <f>I49-BV49</f>
+        <f>I49-H49-SUM(M49:BT49)</f>
         <v/>
       </c>
       <c r="BX49" s="25">
-        <f>IF(I49=0,"",BV49/I49)</f>
+        <f>IF(I49=0,"",(H49+SUM(M49:BT49))/I49)</f>
         <v/>
       </c>
       <c r="BY49" s="26" t="n"/>
@@ -5919,15 +5954,15 @@
       <c r="BT50" s="21" t="n"/>
       <c r="BU50" s="21" t="n"/>
       <c r="BV50" s="24">
-        <f>SUM(M50:BT50)</f>
+        <f>H50+SUM(M50:BT50)</f>
         <v/>
       </c>
       <c r="BW50" s="24">
-        <f>I50-BV50</f>
+        <f>I50-H50-SUM(M50:BT50)</f>
         <v/>
       </c>
       <c r="BX50" s="25">
-        <f>IF(I50=0,"",BV50/I50)</f>
+        <f>IF(I50=0,"",(H50+SUM(M50:BT50))/I50)</f>
         <v/>
       </c>
       <c r="BY50" s="26" t="n"/>
@@ -6016,15 +6051,15 @@
       <c r="BT51" s="21" t="n"/>
       <c r="BU51" s="21" t="n"/>
       <c r="BV51" s="24">
-        <f>SUM(M51:BT51)</f>
+        <f>H51+SUM(M51:BT51)</f>
         <v/>
       </c>
       <c r="BW51" s="24">
-        <f>I51-BV51</f>
+        <f>I51-H51-SUM(M51:BT51)</f>
         <v/>
       </c>
       <c r="BX51" s="25">
-        <f>IF(I51=0,"",BV51/I51)</f>
+        <f>IF(I51=0,"",(H51+SUM(M51:BT51))/I51)</f>
         <v/>
       </c>
       <c r="BY51" s="26" t="n"/>
